--- a/ig/ch-elm/StructureDefinition-ch-elm-codeableconcept.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-codeableconcept.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$10</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="142">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips</t>
+    <t>http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips|2.0.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -357,25 +357,25 @@
 </t>
   </si>
   <si>
-    <t>A reference to a code defined by a terminology system</t>
+    <t>Code defined by a terminology system</t>
   </si>
   <si>
     <t>A reference to a code defined by a terminology system.</t>
   </si>
   <si>
-    <t>Codes may be defined very casually in enumerations or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.</t>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
   </si>
   <si>
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>fhir:Coding rdfs:subClassOf dt:CDCoding</t>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>fhir:CodeableConcept.coding rdfs:subPropertyOf dt:CD.coding</t>
   </si>
   <si>
     <t>CodeableConcept.text</t>
@@ -400,6 +400,58 @@
   </si>
   <si>
     <t>fhir:CodeableConcept.text rdfs:subPropertyOf dt:CD.originalText</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text.id</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text.extension:translation</t>
+  </si>
+  <si>
+    <t>translation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {translation|5.3.0-ballot-tc1}
+</t>
+  </si>
+  <si>
+    <t>Language Translation (Localization)</t>
+  </si>
+  <si>
+    <t>Language translation from base language of resource to another language, used to provide translations for strings, including markdown. Generally, the type of the translation extension SHOULD match that of the element being extended.</t>
+  </si>
+  <si>
+    <t>ST.translation</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text.value</t>
+  </si>
+  <si>
+    <t>Primitive value for string</t>
+  </si>
+  <si>
+    <t>The actual value</t>
+  </si>
+  <si>
+    <t>1048576</t>
+  </si>
+  <si>
+    <t>string.value</t>
   </si>
 </sst>
 </file>
@@ -718,11 +770,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="22.97265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="22.97265625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="35.58203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="26.6015625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -756,7 +808,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="48.5546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="39.109375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="39.890625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="51.734375" customWidth="true" bestFit="true"/>
   </cols>
@@ -1236,7 +1288,7 @@
         <v>77</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>109</v>
@@ -1309,7 +1361,7 @@
         <v>79</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>85</v>
@@ -1437,8 +1489,444 @@
         <v>124</v>
       </c>
     </row>
+    <row r="7" hidden="true">
+      <c r="A7" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K7" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF7" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" hidden="true">
+      <c r="A8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q8" s="2"/>
+      <c r="R8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AC8" s="2"/>
+      <c r="AD8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" hidden="true">
+      <c r="A9" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q9" s="2"/>
+      <c r="R9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AM9" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" hidden="true">
+      <c r="A10" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K10" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH10" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM10" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AM6">
+  <autoFilter ref="A1:AM10">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -1448,7 +1936,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI5">
+  <conditionalFormatting sqref="A2:AI9">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/ch-elm/StructureDefinition-ch-elm-codeableconcept.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-codeableconcept.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-codeableconcept.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-codeableconcept.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-codeableconcept.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-codeableconcept.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
